--- a/input/Кол-во подключений.xlsx
+++ b/input/Кол-во подключений.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
   <si>
     <t>Период</t>
   </si>
@@ -45,21 +45,18 @@
     <t>wram_account_5</t>
   </si>
   <si>
-    <t>kazakov</t>
-  </si>
-  <si>
     <t>lucas</t>
   </si>
   <si>
-    <t>tomas</t>
-  </si>
-  <si>
     <t>alejandro</t>
   </si>
   <si>
     <t>Aloicio</t>
   </si>
   <si>
+    <t>Andrey</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -72,7 +69,7 @@
     <t>Количество подключенных за период</t>
   </si>
   <si>
-    <t>11 июня 2026, 9:01:59</t>
+    <t>22 июня 2026, 14:28:21</t>
   </si>
   <si>
     <t>Фильтры</t>
@@ -81,7 +78,7 @@
     <t>Даты</t>
   </si>
   <si>
-    <t>01.04.2026 - 30.04.2026</t>
+    <t>01.05.2026 - 31.05.2026</t>
   </si>
   <si>
     <t>Тип периода</t>
@@ -479,7 +476,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
@@ -514,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -525,7 +522,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -547,7 +544,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -558,7 +555,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -569,62 +566,51 @@
         <v>8</v>
       </c>
       <c r="C8" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>878372</v>
+        <v>902654</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>902654</v>
+        <v>1105774</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1029766</v>
+        <v>1142021</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1105774</v>
+        <v>1181121</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
-        <v>1142021</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -653,51 +639,51 @@
   <cols>
     <col min="1" max="1" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="39.99" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="26.993" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4550</v>
+        <v>4578</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
